--- a/sms_new_mandeep.xlsx
+++ b/sms_new_mandeep.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="42">
   <si>
     <t xml:space="preserve">No.</t>
   </si>
@@ -52,16 +52,19 @@
     <t xml:space="preserve">Madhukar Verma</t>
   </si>
   <si>
+    <t xml:space="preserve">JKR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGLISH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42729 Mayfair Park Ave Fremont Fremont 94538 California USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David</t>
+  </si>
+  <si>
     <t xml:space="preserve">GG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENGLISH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42729 Mayfair Park Ave Fremont Fremont 94538 California USA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">David</t>
   </si>
   <si>
     <t xml:space="preserve">PO Box 87301, Park Place, Houston, Texas</t>
@@ -441,7 +444,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K30"/>
-  <sheetFormatPr defaultColWidth="11.78515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.8046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="34.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="40.85"/>
@@ -546,16 +549,16 @@
         <v>13</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" s="10"/>
       <c r="I5" s="4"/>
@@ -570,19 +573,19 @@
         <v>45154</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H6" s="10"/>
       <c r="I6" s="4"/>
@@ -597,19 +600,19 @@
         <v>45154</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H7" s="10"/>
       <c r="I7" s="4"/>
@@ -694,10 +697,10 @@
       <c r="H13" s="10"/>
       <c r="I13" s="4"/>
       <c r="J13" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -711,10 +714,10 @@
       <c r="H14" s="10"/>
       <c r="I14" s="4"/>
       <c r="J14" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K14" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -728,10 +731,10 @@
       <c r="H15" s="10"/>
       <c r="I15" s="4"/>
       <c r="J15" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -745,10 +748,10 @@
       <c r="H16" s="10"/>
       <c r="I16" s="4"/>
       <c r="J16" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -762,10 +765,10 @@
       <c r="H17" s="10"/>
       <c r="I17" s="4"/>
       <c r="J17" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -779,10 +782,10 @@
       <c r="H18" s="10"/>
       <c r="I18" s="4"/>
       <c r="J18" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -796,10 +799,10 @@
       <c r="H19" s="10"/>
       <c r="I19" s="4"/>
       <c r="J19" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -813,10 +816,10 @@
       <c r="H20" s="10"/>
       <c r="I20" s="4"/>
       <c r="J20" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -830,10 +833,10 @@
       <c r="H21" s="10"/>
       <c r="I21" s="4"/>
       <c r="J21" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K21" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -847,10 +850,10 @@
       <c r="H22" s="10"/>
       <c r="I22" s="4"/>
       <c r="J22" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K22" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -864,10 +867,10 @@
       <c r="H23" s="10"/>
       <c r="I23" s="4"/>
       <c r="J23" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -881,10 +884,10 @@
       <c r="H24" s="10"/>
       <c r="I24" s="4"/>
       <c r="J24" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K24" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -898,10 +901,10 @@
       <c r="H25" s="10"/>
       <c r="I25" s="4"/>
       <c r="J25" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K25" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -915,10 +918,10 @@
       <c r="H26" s="10"/>
       <c r="I26" s="4"/>
       <c r="J26" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K26" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -932,10 +935,10 @@
       <c r="H27" s="10"/>
       <c r="I27" s="4"/>
       <c r="J27" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K27" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -949,10 +952,10 @@
       <c r="H28" s="10"/>
       <c r="I28" s="4"/>
       <c r="J28" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K28" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -966,10 +969,10 @@
       <c r="H29" s="10"/>
       <c r="I29" s="4"/>
       <c r="J29" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K29" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -983,10 +986,10 @@
       <c r="H30" s="10"/>
       <c r="I30" s="4"/>
       <c r="J30" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K30" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
